--- a/artfynd/A 13395-2024 artfynd.xlsx
+++ b/artfynd/A 13395-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121691927</v>
+        <v>121690958</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,11 +713,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514729</v>
+        <v>514564</v>
       </c>
       <c r="R2" t="n">
-        <v>6584809</v>
+        <v>6584853</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -759,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121690958</v>
+        <v>121690954</v>
       </c>
       <c r="B3" t="n">
         <v>57726</v>
@@ -854,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514564</v>
+        <v>514708</v>
       </c>
       <c r="R3" t="n">
-        <v>6584853</v>
+        <v>6584777</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121690954</v>
+        <v>121691927</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>57898</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,16 +941,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -968,6 +963,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514708</v>
+        <v>514729</v>
       </c>
       <c r="R4" t="n">
-        <v>6584777</v>
+        <v>6584809</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1009,22 +1009,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 13395-2024 artfynd.xlsx
+++ b/artfynd/A 13395-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121690958</v>
+        <v>121690954</v>
       </c>
       <c r="B2" t="n">
         <v>57726</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514564</v>
+        <v>514708</v>
       </c>
       <c r="R2" t="n">
-        <v>6584853</v>
+        <v>6584777</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121690954</v>
+        <v>121691927</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>57898</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,6 +838,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -849,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514708</v>
+        <v>514729</v>
       </c>
       <c r="R3" t="n">
-        <v>6584777</v>
+        <v>6584809</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -879,22 +884,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121691927</v>
+        <v>121690958</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,16 +946,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,11 +968,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514729</v>
+        <v>514564</v>
       </c>
       <c r="R4" t="n">
-        <v>6584809</v>
+        <v>6584853</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1009,22 +1009,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 13395-2024 artfynd.xlsx
+++ b/artfynd/A 13395-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121690954</v>
+        <v>121691927</v>
       </c>
       <c r="B2" t="n">
-        <v>57726</v>
+        <v>57898</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,6 +713,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514708</v>
+        <v>514729</v>
       </c>
       <c r="R2" t="n">
-        <v>6584777</v>
+        <v>6584809</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -754,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121691927</v>
+        <v>121690954</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +821,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,11 +843,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514729</v>
+        <v>514708</v>
       </c>
       <c r="R3" t="n">
-        <v>6584809</v>
+        <v>6584777</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -884,22 +884,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 13395-2024 artfynd.xlsx
+++ b/artfynd/A 13395-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121691927</v>
+        <v>121690954</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,11 +713,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514729</v>
+        <v>514708</v>
       </c>
       <c r="R2" t="n">
-        <v>6584809</v>
+        <v>6584777</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -759,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121690954</v>
+        <v>121691927</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>57898</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -843,6 +838,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514708</v>
+        <v>514729</v>
       </c>
       <c r="R3" t="n">
-        <v>6584777</v>
+        <v>6584809</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -884,22 +884,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 13395-2024 artfynd.xlsx
+++ b/artfynd/A 13395-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121691927</v>
+        <v>121690958</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57734</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,11 +713,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514729</v>
+        <v>514564</v>
       </c>
       <c r="R2" t="n">
-        <v>6584809</v>
+        <v>6584853</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -759,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121690954</v>
+        <v>121691927</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>57906</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -843,6 +838,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514708</v>
+        <v>514729</v>
       </c>
       <c r="R3" t="n">
-        <v>6584777</v>
+        <v>6584809</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -884,22 +884,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -930,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121690958</v>
+        <v>121690954</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>57734</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514564</v>
+        <v>514708</v>
       </c>
       <c r="R4" t="n">
-        <v>6584853</v>
+        <v>6584777</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13395-2024 artfynd.xlsx
+++ b/artfynd/A 13395-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121690958</v>
+        <v>121691927</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57906</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,6 +713,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514564</v>
+        <v>514729</v>
       </c>
       <c r="R2" t="n">
-        <v>6584853</v>
+        <v>6584809</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -754,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121691927</v>
+        <v>121690958</v>
       </c>
       <c r="B3" t="n">
-        <v>57906</v>
+        <v>57734</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,16 +821,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,11 +843,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514729</v>
+        <v>514564</v>
       </c>
       <c r="R3" t="n">
-        <v>6584809</v>
+        <v>6584853</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -884,22 +884,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 13395-2024 artfynd.xlsx
+++ b/artfynd/A 13395-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121691927</v>
+        <v>121690958</v>
       </c>
       <c r="B2" t="n">
-        <v>57906</v>
+        <v>57734</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,11 +713,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514729</v>
+        <v>514564</v>
       </c>
       <c r="R2" t="n">
-        <v>6584809</v>
+        <v>6584853</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -759,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121690958</v>
+        <v>121691927</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>57906</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,16 +816,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -843,6 +838,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514564</v>
+        <v>514729</v>
       </c>
       <c r="R3" t="n">
-        <v>6584853</v>
+        <v>6584809</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -884,22 +884,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 13395-2024 artfynd.xlsx
+++ b/artfynd/A 13395-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121690958</v>
+        <v>121690954</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514564</v>
+        <v>514708</v>
       </c>
       <c r="R2" t="n">
-        <v>6584853</v>
+        <v>6584777</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,7 +803,7 @@
         <v>121691927</v>
       </c>
       <c r="B3" t="n">
-        <v>57906</v>
+        <v>57910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121690954</v>
+        <v>121690958</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>57738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514708</v>
+        <v>514564</v>
       </c>
       <c r="R4" t="n">
-        <v>6584777</v>
+        <v>6584853</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13395-2024 artfynd.xlsx
+++ b/artfynd/A 13395-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121690954</v>
+        <v>121691927</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,6 +708,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514708</v>
+        <v>514729</v>
       </c>
       <c r="R2" t="n">
-        <v>6584777</v>
+        <v>6584809</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,19 +800,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121691927</v>
+        <v>121691942</v>
       </c>
       <c r="B3" t="n">
-        <v>57910</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -838,11 +833,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -854,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514729</v>
+        <v>514722</v>
       </c>
       <c r="R3" t="n">
-        <v>6584809</v>
+        <v>6584832</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -930,15 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121690958</v>
+        <v>121690893</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,6 +953,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -979,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514564</v>
+        <v>514649</v>
       </c>
       <c r="R4" t="n">
-        <v>6584853</v>
+        <v>6584845</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1034,370 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Alight  - Dylta bruk 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121690954</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brunnsjötorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>514708</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6584777</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Ola Erlandsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Alight  - Dylta bruk 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121690955</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brunnsjötorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>514677</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6584740</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ola Erlandsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Alight  - Dylta bruk 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121690958</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brunnsjötorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>514564</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6584853</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ola Erlandsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Alight  - Dylta bruk 2</t>
         </is>

--- a/artfynd/A 13395-2024 artfynd.xlsx
+++ b/artfynd/A 13395-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Alight  - Dylta bruk 2</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121691927</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
           <t>Alight  - Dylta bruk 2</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121691942</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1042,6 +1057,11 @@
           <t>Alight  - Dylta bruk 2</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121690893</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1162,6 +1182,11 @@
           <t>Alight  - Dylta bruk 2</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121690954</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,6 +1307,11 @@
           <t>Alight  - Dylta bruk 2</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121690955</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1402,8 +1432,21 @@
           <t>Alight  - Dylta bruk 2</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121690958</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>